--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:10:08+00:00</t>
+    <t>2026-09-03T05:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:17:43+00:00</t>
+    <t>2026-09-03T05:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:48:26+00:00</t>
+    <t>2026-09-03T10:47:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:47:18+00:00</t>
+    <t>2026-09-08T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-alpha.6</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:02:02+00:00</t>
+    <t>2026-09-09T10:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:10:08+00:00</t>
+    <t>2026-09-09T13:56:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:56:56+00:00</t>
+    <t>2026-09-09T14:11:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:11:38+00:00</t>
+    <t>2026-09-09T14:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:19:13+00:00</t>
+    <t>2026-09-09T14:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-barlett-score.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:42:29+00:00</t>
+    <t>2026-09-09T15:55:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
